--- a/scripts/questions_test.xlsx
+++ b/scripts/questions_test.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:K61"/>
   <cols>
     <col min="1" max="1" width="55.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -407,6 +407,9 @@
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,16 +437,25 @@
       <c r="H1" t="str">
         <v>isActive</v>
       </c>
+      <c r="I1" t="str">
+        <v>bfiItemNo</v>
+      </c>
+      <c r="J1" t="str">
+        <v>bfiReverse</v>
+      </c>
+      <c r="K1" t="str">
+        <v>bfiFacet</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>某智能制造实验室邀请你用编程控制机械臂组装零件，这让你感到？</v>
+        <v>我是一个……的人 1. 性格外向，喜欢交际</v>
       </c>
       <c r="B2" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C2" t="str">
-        <v>R</v>
+        <v>E</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -459,17 +471,26 @@
       </c>
       <c r="H2" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="str">
+        <v>N</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Sociability</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>一场无人机竞速赛需要维修团队，负责赛后故障排查与修复，你愿意加入吗？</v>
+        <v>我是一个……的人 2. 心肠柔软，有同情心</v>
       </c>
       <c r="B3" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C3" t="str">
-        <v>R</v>
+        <v>A</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -485,17 +506,26 @@
       </c>
       <c r="H3" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="str">
+        <v>N</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Compassion</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>团队需要有人学习操作3D打印机制作产品原型，你会主动承担吗？</v>
+        <v>我是一个……的人 3. 缺乏条理</v>
       </c>
       <c r="B4" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C4" t="str">
-        <v>R</v>
+        <v>C</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -511,43 +541,61 @@
       </c>
       <c r="H4" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Organization</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>公司为你配备了AR眼镜用于指导设备安装，你最可能会主动探索它吗？</v>
+        <v>我是一个……的人 4. 从容，善于处理压力</v>
       </c>
       <c r="B5" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C5" t="str">
-        <v>R</v>
+        <v>N</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>male</v>
+        <v>both</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>45</v>
+        <v>999</v>
       </c>
       <c r="H5" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Anxiety</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>一份远程办公对创意员工效率影响的数据集摆在你面前，你想深入挖掘吗？</v>
+        <v>我是一个……的人 5. 对艺术没有什么兴趣</v>
       </c>
       <c r="B6" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C6" t="str">
-        <v>I</v>
+        <v>O</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -563,17 +611,26 @@
       </c>
       <c r="H6" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K6" t="str">
+        <v>AestheticSensitivity</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>公司AI系统给出意外预测结果，没人能解释，你会主动追查原因吗？</v>
+        <v>我是一个……的人 6. 性格坚定自信，敢于表达自己的观点</v>
       </c>
       <c r="B7" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C7" t="str">
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -589,17 +646,26 @@
       </c>
       <c r="H7" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="str">
+        <v>N</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Assertiveness</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>你发现新算法可能提升效率30%，但需大量时间验证，你愿意投入吗？</v>
+        <v>我是一个……的人 7. 为人恭谦，尊重他人</v>
       </c>
       <c r="B8" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C8" t="str">
-        <v>I</v>
+        <v>A</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -615,17 +681,26 @@
       </c>
       <c r="H8" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="str">
+        <v>N</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Respectfulness</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>面对复杂的用户行为分析任务，你倾向于先拆解数据框架再动手吗？</v>
+        <v>我是一个……的人 8. 比较懒</v>
       </c>
       <c r="B9" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C9" t="str">
-        <v>I</v>
+        <v>C</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -634,24 +709,33 @@
         <v>both</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>999</v>
       </c>
       <c r="H9" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Productiveness</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>公司品牌视觉需全面重新设计以适应AI时代审美，你愿意主导这个项目吗？</v>
+        <v>我是一个……的人 9. 经历挫折后仍能保持积极心态</v>
       </c>
       <c r="B10" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C10" t="str">
-        <v>A</v>
+        <v>N</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -667,17 +751,26 @@
       </c>
       <c r="H10" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Depression</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>一个虚拟展览需要你用生成式AI工具创作概念图，你对这个任务感兴趣吗？</v>
+        <v>我是一个……的人 10. 对许多不同的事物都感兴趣</v>
       </c>
       <c r="B11" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C11" t="str">
-        <v>A</v>
+        <v>O</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -693,40 +786,58 @@
       </c>
       <c r="H11" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" t="str">
+        <v>N</v>
+      </c>
+      <c r="K11" t="str">
+        <v>IntellectualCuriosity</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>有机会从色彩到排版完全主导一款新应用的界面设计，你的感受是？</v>
+        <v>我是一个……的人 11. 很少觉得兴奋或者特别想要(做)什么</v>
       </c>
       <c r="B12" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C12" t="str">
-        <v>A</v>
+        <v>E</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="str">
-        <v>female</v>
+        <v>both</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>40</v>
+        <v>999</v>
       </c>
       <c r="H12" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Energy</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>团队需要人撰写公司年度报告的创意叙事文案，你会主动接手吗？</v>
+        <v>我是一个……的人 12. 常常挑别人的毛病</v>
       </c>
       <c r="B13" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C13" t="str">
         <v>A</v>
@@ -746,16 +857,25 @@
       <c r="H13" t="str">
         <v>TRUE</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Trust</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>新来的实习生对远程协作工具不熟悉，你会主动带他们上手吗？</v>
+        <v>我是一个……的人 13. 可信赖的，可靠的</v>
       </c>
       <c r="B14" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C14" t="str">
-        <v>S</v>
+        <v>C</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -771,17 +891,26 @@
       </c>
       <c r="H14" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
+      <c r="J14" t="str">
+        <v>N</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Responsibility</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>团队成员因工作方式分歧产生矛盾，有人找你调解，你会积极参与吗？</v>
+        <v>我是一个……的人 14. 喜怒无常，情绪起伏较多</v>
       </c>
       <c r="B15" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C15" t="str">
-        <v>S</v>
+        <v>N</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -797,17 +926,26 @@
       </c>
       <c r="H15" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
+      <c r="J15" t="str">
+        <v>N</v>
+      </c>
+      <c r="K15" t="str">
+        <v>EmotionalVolatility</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>有机会为公司设计一套AI工具使用培训方案，你觉得这份工作有意义吗？</v>
+        <v>我是一个……的人 15. 善于创造，能找到聪明的方法来做事</v>
       </c>
       <c r="B16" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C16" t="str">
-        <v>S</v>
+        <v>O</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -823,17 +961,26 @@
       </c>
       <c r="H16" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
+      <c r="J16" t="str">
+        <v>N</v>
+      </c>
+      <c r="K16" t="str">
+        <v>CreativeImagination</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>需要组织用户焦点小组访谈来收集产品反馈，你愿意主持这个过程吗？</v>
+        <v>我是一个……的人 16. 比较安静</v>
       </c>
       <c r="B17" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C17" t="str">
-        <v>S</v>
+        <v>E</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -849,17 +996,26 @@
       </c>
       <c r="H17" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Sociability</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>你发现公司在某个AI新市场有巨大机会但无人推动，你会站出来吗？</v>
+        <v>我是一个……的人 17. 对他人没有什么同情心</v>
       </c>
       <c r="B18" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C18" t="str">
-        <v>E</v>
+        <v>A</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -868,24 +1024,33 @@
         <v>both</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>999</v>
       </c>
       <c r="H18" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Compassion</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>远程团队会议陷入僵局，你最可能主动打破沉默、推进讨论吗？</v>
+        <v>我是一个……的人 18. 做事有计划有条理</v>
       </c>
       <c r="B19" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C19" t="str">
-        <v>E</v>
+        <v>C</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -901,43 +1066,61 @@
       </c>
       <c r="H19" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I19">
+        <v>18</v>
+      </c>
+      <c r="J19" t="str">
+        <v>N</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Organization</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>你被提名负责一个跨部门数字化转型项目，你充满期待吗？</v>
+        <v>我是一个……的人 19. 容易紧张</v>
       </c>
       <c r="B20" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C20" t="str">
-        <v>E</v>
+        <v>N</v>
       </c>
       <c r="D20">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="str">
         <v>both</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>999</v>
       </c>
       <c r="H20" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
+      <c r="J20" t="str">
+        <v>N</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Anxiety</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>有机会向投资人展示团队新业务方向，你愿意主导这次路演吗？</v>
+        <v>我是一个……的人 20. 着迷于艺术、音乐或文学</v>
       </c>
       <c r="B21" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C21" t="str">
-        <v>E</v>
+        <v>O</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -953,17 +1136,26 @@
       </c>
       <c r="H21" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I21">
+        <v>20</v>
+      </c>
+      <c r="J21" t="str">
+        <v>N</v>
+      </c>
+      <c r="K21" t="str">
+        <v>AestheticSensitivity</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>公司要求制定AI工具使用规范手册，包含所有操作流程，你愿意主导吗？</v>
+        <v>我是一个……的人 21. 常常处于主导地位，像个领导一样</v>
       </c>
       <c r="B22" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C22" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -979,17 +1171,26 @@
       </c>
       <c r="H22" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I22">
+        <v>21</v>
+      </c>
+      <c r="J22" t="str">
+        <v>N</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Assertiveness</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>财务系统升级需整理历史数据并建立新分类标准，你觉得这类任务有价值吗？</v>
+        <v>我是一个……的人 22. 常与他人意见不和</v>
       </c>
       <c r="B23" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C23" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1005,14 +1206,23 @@
       </c>
       <c r="H23" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I23">
+        <v>22</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Respectfulness</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>团队项目管理混乱，你有机会重新梳理所有任务和截止日期，你会主动吗？</v>
+        <v>我是一个……的人 23. 很难开始行动起来去完成一项任务</v>
       </c>
       <c r="B24" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C24" t="str">
         <v>C</v>
@@ -1032,16 +1242,25 @@
       <c r="H24" t="str">
         <v>TRUE</v>
       </c>
+      <c r="I24">
+        <v>23</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Productiveness</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>每月整理并分析远程团队的工作量报表，你觉得这份工作令你满意吗？</v>
+        <v>我是一个……的人 24. 觉得有安全感，对自己满意</v>
       </c>
       <c r="B25" t="str">
-        <v>RIASEC</v>
+        <v>BIG5</v>
       </c>
       <c r="C25" t="str">
-        <v>C</v>
+        <v>N</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1057,11 +1276,20 @@
       </c>
       <c r="H25" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I25">
+        <v>24</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Depression</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>当你遇到从未使用过的AI工具时，你的第一反应是立刻尝试吗？</v>
+        <v>我是一个……的人 25. 不喜欢知识性或者哲学性强的讨论</v>
       </c>
       <c r="B26" t="str">
         <v>BIG5</v>
@@ -1084,16 +1312,25 @@
       <c r="H26" t="str">
         <v>TRUE</v>
       </c>
+      <c r="I26">
+        <v>25</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K26" t="str">
+        <v>IntellectualCuriosity</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>同事提出完全颠覆传统工作流程的新方案，你倾向于支持探索吗？</v>
+        <v>我是一个……的人 26. 不如别人有活力</v>
       </c>
       <c r="B27" t="str">
         <v>BIG5</v>
       </c>
       <c r="C27" t="str">
-        <v>O</v>
+        <v>E</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1109,17 +1346,26 @@
       </c>
       <c r="H27" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I27">
+        <v>26</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Energy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>你是否经常主动思考某个行业在10年内可能发生的根本性变化？</v>
+        <v>我是一个……的人 27. 宽宏大量</v>
       </c>
       <c r="B28" t="str">
         <v>BIG5</v>
       </c>
       <c r="C28" t="str">
-        <v>O</v>
+        <v>A</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1135,17 +1381,26 @@
       </c>
       <c r="H28" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I28">
+        <v>27</v>
+      </c>
+      <c r="J28" t="str">
+        <v>N</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Trust</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>面对量子计算等抽象技术概念，你会感到好奇并主动学习吗？</v>
+        <v>我是一个……的人 28. 有时比较没有责任心</v>
       </c>
       <c r="B29" t="str">
         <v>BIG5</v>
       </c>
       <c r="C29" t="str">
-        <v>O</v>
+        <v>C</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1161,17 +1416,26 @@
       </c>
       <c r="H29" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I29">
+        <v>28</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Responsibility</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>在远程办公、无人监督的环境下，你依然能保持高效的工作状态吗？</v>
+        <v>我是一个……的人 29. 情绪稳定，不易生气</v>
       </c>
       <c r="B30" t="str">
         <v>BIG5</v>
       </c>
       <c r="C30" t="str">
-        <v>C</v>
+        <v>N</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1187,17 +1451,26 @@
       </c>
       <c r="H30" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I30">
+        <v>29</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K30" t="str">
+        <v>EmotionalVolatility</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>接手细节繁多的长期项目时，你会第一步就制定详细计划吗？</v>
+        <v>我是一个……的人 30. 几乎没有什么创造性</v>
       </c>
       <c r="B31" t="str">
         <v>BIG5</v>
       </c>
       <c r="C31" t="str">
-        <v>C</v>
+        <v>O</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1213,17 +1486,26 @@
       </c>
       <c r="H31" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I31">
+        <v>30</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K31" t="str">
+        <v>CreativeImagination</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>项目还剩两周、进度已达80%时，你会维持高强度推进直到完成吗？</v>
+        <v>我是一个……的人 31. 有时会害羞，比较内向</v>
       </c>
       <c r="B32" t="str">
         <v>BIG5</v>
       </c>
       <c r="C32" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1239,17 +1521,26 @@
       </c>
       <c r="H32" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I32">
+        <v>31</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Sociability</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>你在某任务中发现了一个小错误，修复它需要额外3小时，你会立刻处理吗？</v>
+        <v>我是一个……的人 32. 乐于助人，待人无私</v>
       </c>
       <c r="B33" t="str">
         <v>BIG5</v>
       </c>
       <c r="C33" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1265,17 +1556,26 @@
       </c>
       <c r="H33" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I33">
+        <v>32</v>
+      </c>
+      <c r="J33" t="str">
+        <v>N</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Compassion</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>一个需要持续与10+客户沟通的新项目找到你，你感到精力充沛吗？</v>
+        <v>我是一个……的人 33. 习惯让事物保持整洁有序</v>
       </c>
       <c r="B34" t="str">
         <v>BIG5</v>
       </c>
       <c r="C34" t="str">
-        <v>E</v>
+        <v>C</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1291,17 +1591,26 @@
       </c>
       <c r="H34" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I34">
+        <v>33</v>
+      </c>
+      <c r="J34" t="str">
+        <v>N</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Organization</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>公司组织线下行业交流活动，你通常会主动拓展新联系吗？</v>
+        <v>我是一个……的人 34. 时常忧心忡忡，担心很多事情</v>
       </c>
       <c r="B35" t="str">
         <v>BIG5</v>
       </c>
       <c r="C35" t="str">
-        <v>E</v>
+        <v>N</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1317,17 +1626,26 @@
       </c>
       <c r="H35" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I35">
+        <v>34</v>
+      </c>
+      <c r="J35" t="str">
+        <v>N</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Anxiety</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>在陌生线上会议中主持人突然请你发言，你能轻松应对吗？</v>
+        <v>我是一个……的人 35. 重视艺术与审美</v>
       </c>
       <c r="B36" t="str">
         <v>BIG5</v>
       </c>
       <c r="C36" t="str">
-        <v>E</v>
+        <v>O</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1343,11 +1661,20 @@
       </c>
       <c r="H36" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I36">
+        <v>35</v>
+      </c>
+      <c r="J36" t="str">
+        <v>N</v>
+      </c>
+      <c r="K36" t="str">
+        <v>AestheticSensitivity</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>午休时间你更倾向于和同事交流而非独处充电吗？</v>
+        <v>我是一个……的人 36. 感觉自己很难对他人产生影响</v>
       </c>
       <c r="B37" t="str">
         <v>BIG5</v>
@@ -1370,10 +1697,19 @@
       <c r="H37" t="str">
         <v>TRUE</v>
       </c>
+      <c r="I37">
+        <v>36</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Assertiveness</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>同事的方案有明显缺陷但他非常投入，你在会议上会温和提出建议吗？</v>
+        <v>我是一个……的人 37. 有时对人比较粗鲁</v>
       </c>
       <c r="B38" t="str">
         <v>BIG5</v>
@@ -1396,16 +1732,25 @@
       <c r="H38" t="str">
         <v>TRUE</v>
       </c>
+      <c r="I38">
+        <v>37</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Respectfulness</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>你发现团队某成员压力极大，虽不在你职责范围，你会主动提供支持吗？</v>
+        <v>我是一个……的人 38. 有效率，做事有始有终</v>
       </c>
       <c r="B39" t="str">
         <v>BIG5</v>
       </c>
       <c r="C39" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1421,17 +1766,26 @@
       </c>
       <c r="H39" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I39">
+        <v>38</v>
+      </c>
+      <c r="J39" t="str">
+        <v>N</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Productiveness</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>你的意见与团队多数人不同时，你倾向于为和谐而妥协吗？</v>
+        <v>我是一个……的人 39. 时常觉得悲伤</v>
       </c>
       <c r="B40" t="str">
         <v>BIG5</v>
       </c>
       <c r="C40" t="str">
-        <v>A</v>
+        <v>N</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1447,17 +1801,26 @@
       </c>
       <c r="H40" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I40">
+        <v>39</v>
+      </c>
+      <c r="J40" t="str">
+        <v>N</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Depression</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>合作客户提出你认为不合理的要求，你会优先考虑维护关系吗？</v>
+        <v>我是一个……的人 40. 思想深刻</v>
       </c>
       <c r="B41" t="str">
         <v>BIG5</v>
       </c>
       <c r="C41" t="str">
-        <v>A</v>
+        <v>O</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1473,17 +1836,26 @@
       </c>
       <c r="H41" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I41">
+        <v>40</v>
+      </c>
+      <c r="J41" t="str">
+        <v>N</v>
+      </c>
+      <c r="K41" t="str">
+        <v>IntellectualCuriosity</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>项目出现重大变更、所有计划需重来时，你会感到强烈焦虑吗？</v>
+        <v>我是一个……的人 41. 精力充沛</v>
       </c>
       <c r="B42" t="str">
         <v>BIG5</v>
       </c>
       <c r="C42" t="str">
-        <v>N</v>
+        <v>E</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1499,17 +1871,26 @@
       </c>
       <c r="H42" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I42">
+        <v>41</v>
+      </c>
+      <c r="J42" t="str">
+        <v>N</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Energy</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>连续两周高强度工作压力下，你通常很难保持情绪平稳吗？</v>
+        <v>我是一个……的人 42. 不相信别人，怀疑别人的意图</v>
       </c>
       <c r="B43" t="str">
         <v>BIG5</v>
       </c>
       <c r="C43" t="str">
-        <v>N</v>
+        <v>A</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1525,17 +1906,26 @@
       </c>
       <c r="H43" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Trust</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>工作中犯了影响较大的错误后，你会反复自责很长时间吗？</v>
+        <v>我是一个……的人 43. 可靠的，总是值得他人信赖</v>
       </c>
       <c r="B44" t="str">
         <v>BIG5</v>
       </c>
       <c r="C44" t="str">
-        <v>N</v>
+        <v>C</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1551,11 +1941,20 @@
       </c>
       <c r="H44" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I44">
+        <v>43</v>
+      </c>
+      <c r="J44" t="str">
+        <v>N</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Responsibility</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>面对频繁变更的需求和工作中的不确定性，你会感到明显不适吗？</v>
+        <v>我是一个……的人 44. 能够控制自己的情绪</v>
       </c>
       <c r="B45" t="str">
         <v>BIG5</v>
@@ -1577,11 +1976,580 @@
       </c>
       <c r="H45" t="str">
         <v>TRUE</v>
+      </c>
+      <c r="I45">
+        <v>44</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K45" t="str">
+        <v>EmotionalVolatility</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>我是一个……的人 45. 缺乏想象力</v>
+      </c>
+      <c r="B46" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C46" t="str">
+        <v>O</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="str">
+        <v>both</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>999</v>
+      </c>
+      <c r="H46" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I46">
+        <v>45</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K46" t="str">
+        <v>CreativeImagination</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>我是一个……的人 46. 爱说话，健谈</v>
+      </c>
+      <c r="B47" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C47" t="str">
+        <v>E</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="str">
+        <v>both</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>999</v>
+      </c>
+      <c r="H47" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I47">
+        <v>46</v>
+      </c>
+      <c r="J47" t="str">
+        <v>N</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Sociability</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>我是一个……的人 47. 有时对人冷淡，漠不关心</v>
+      </c>
+      <c r="B48" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C48" t="str">
+        <v>A</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="str">
+        <v>both</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>999</v>
+      </c>
+      <c r="H48" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I48">
+        <v>47</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Compassion</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>我是一个……的人 48. 乱糟糟的，不爱收拾</v>
+      </c>
+      <c r="B49" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C49" t="str">
+        <v>C</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="str">
+        <v>both</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>999</v>
+      </c>
+      <c r="H49" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I49">
+        <v>48</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Organization</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>我是一个……的人 49. 很少觉得焦虑或者害怕</v>
+      </c>
+      <c r="B50" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C50" t="str">
+        <v>N</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="str">
+        <v>both</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>999</v>
+      </c>
+      <c r="H50" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I50">
+        <v>49</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Anxiety</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>我是一个……的人 50. 觉得诗歌、戏剧很无聊</v>
+      </c>
+      <c r="B51" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C51" t="str">
+        <v>O</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="str">
+        <v>both</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>999</v>
+      </c>
+      <c r="H51" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I51">
+        <v>50</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K51" t="str">
+        <v>AestheticSensitivity</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>我是一个……的人 51. 更喜欢让别人来领头负责</v>
+      </c>
+      <c r="B52" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C52" t="str">
+        <v>E</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="str">
+        <v>both</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>999</v>
+      </c>
+      <c r="H52" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I52">
+        <v>51</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Assertiveness</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>我是一个……的人 52. 待人谦逊礼让</v>
+      </c>
+      <c r="B53" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C53" t="str">
+        <v>A</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="str">
+        <v>both</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>999</v>
+      </c>
+      <c r="H53" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I53">
+        <v>52</v>
+      </c>
+      <c r="J53" t="str">
+        <v>N</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Respectfulness</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>我是一个……的人 53. 有恒心，能坚持把事情做完</v>
+      </c>
+      <c r="B54" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C54" t="str">
+        <v>C</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" t="str">
+        <v>both</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>999</v>
+      </c>
+      <c r="H54" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I54">
+        <v>53</v>
+      </c>
+      <c r="J54" t="str">
+        <v>N</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Productiveness</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>我是一个……的人 54. 时常觉得郁郁寡欢</v>
+      </c>
+      <c r="B55" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C55" t="str">
+        <v>N</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="str">
+        <v>both</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>999</v>
+      </c>
+      <c r="H55" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I55">
+        <v>54</v>
+      </c>
+      <c r="J55" t="str">
+        <v>N</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Depression</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>我是一个……的人 55. 对抽象的概念和想法没什么兴趣</v>
+      </c>
+      <c r="B56" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C56" t="str">
+        <v>O</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="str">
+        <v>both</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>999</v>
+      </c>
+      <c r="H56" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I56">
+        <v>55</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K56" t="str">
+        <v>IntellectualCuriosity</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>我是一个……的人 56. 充满热情</v>
+      </c>
+      <c r="B57" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C57" t="str">
+        <v>E</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" t="str">
+        <v>both</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>999</v>
+      </c>
+      <c r="H57" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I57">
+        <v>56</v>
+      </c>
+      <c r="J57" t="str">
+        <v>N</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Energy</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>我是一个……的人 57. 把人往最好的方面想</v>
+      </c>
+      <c r="B58" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C58" t="str">
+        <v>A</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="str">
+        <v>both</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>999</v>
+      </c>
+      <c r="H58" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I58">
+        <v>57</v>
+      </c>
+      <c r="J58" t="str">
+        <v>N</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Trust</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>我是一个……的人 58. 有时候会做出一些不负责任的行为</v>
+      </c>
+      <c r="B59" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C59" t="str">
+        <v>C</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="str">
+        <v>both</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>999</v>
+      </c>
+      <c r="H59" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I59">
+        <v>58</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Responsibility</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>我是一个……的人 59. 情绪多变，容易愤怒</v>
+      </c>
+      <c r="B60" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C60" t="str">
+        <v>N</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="str">
+        <v>both</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>999</v>
+      </c>
+      <c r="H60" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I60">
+        <v>59</v>
+      </c>
+      <c r="J60" t="str">
+        <v>N</v>
+      </c>
+      <c r="K60" t="str">
+        <v>EmotionalVolatility</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>我是一个……的人 60. 有创意，能想出新点子</v>
+      </c>
+      <c r="B61" t="str">
+        <v>BIG5</v>
+      </c>
+      <c r="C61" t="str">
+        <v>O</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="str">
+        <v>both</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>999</v>
+      </c>
+      <c r="H61" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="I61">
+        <v>60</v>
+      </c>
+      <c r="J61" t="str">
+        <v>N</v>
+      </c>
+      <c r="K61" t="str">
+        <v>CreativeImagination</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/questions_test.xlsx
+++ b/scripts/questions_test.xlsx
@@ -449,7 +449,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>我是一个……的人 1. 性格外向，喜欢交际</v>
+        <v>我是一个性格外向，喜欢交际的人</v>
       </c>
       <c r="B2" t="str">
         <v>BIG5</v>
@@ -484,7 +484,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>我是一个……的人 2. 心肠柔软，有同情心</v>
+        <v>我是一个心肠柔软，有同情心的人</v>
       </c>
       <c r="B3" t="str">
         <v>BIG5</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>我是一个……的人 3. 缺乏条理</v>
+        <v>我是一个缺乏条理的人</v>
       </c>
       <c r="B4" t="str">
         <v>BIG5</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>我是一个……的人 4. 从容，善于处理压力</v>
+        <v>我是一个从容，善于处理压力的人</v>
       </c>
       <c r="B5" t="str">
         <v>BIG5</v>
@@ -589,7 +589,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>我是一个……的人 5. 对艺术没有什么兴趣</v>
+        <v>我是一个对艺术没有什么兴趣的人</v>
       </c>
       <c r="B6" t="str">
         <v>BIG5</v>
@@ -624,7 +624,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>我是一个……的人 6. 性格坚定自信，敢于表达自己的观点</v>
+        <v>我是一个性格坚定自信，敢于表达自己的观点的人</v>
       </c>
       <c r="B7" t="str">
         <v>BIG5</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>我是一个……的人 7. 为人恭谦，尊重他人</v>
+        <v>我是一个为人恭谦，尊重他人的人</v>
       </c>
       <c r="B8" t="str">
         <v>BIG5</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>我是一个……的人 8. 比较懒</v>
+        <v>我是一个比较懒的人</v>
       </c>
       <c r="B9" t="str">
         <v>BIG5</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>我是一个……的人 9. 经历挫折后仍能保持积极心态</v>
+        <v>我是一个经历挫折后仍能保持积极心态的人</v>
       </c>
       <c r="B10" t="str">
         <v>BIG5</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>我是一个……的人 10. 对许多不同的事物都感兴趣</v>
+        <v>我是一个对许多不同的事物都感兴趣的人</v>
       </c>
       <c r="B11" t="str">
         <v>BIG5</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>我是一个……的人 11. 很少觉得兴奋或者特别想要(做)什么</v>
+        <v>我是一个很少觉得兴奋或者特别想要(做)什么的人</v>
       </c>
       <c r="B12" t="str">
         <v>BIG5</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>我是一个……的人 12. 常常挑别人的毛病</v>
+        <v>我是一个常常挑别人的毛病的人</v>
       </c>
       <c r="B13" t="str">
         <v>BIG5</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>我是一个……的人 13. 可信赖的，可靠的</v>
+        <v>我是一个可信赖的，可靠的的人</v>
       </c>
       <c r="B14" t="str">
         <v>BIG5</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>我是一个……的人 14. 喜怒无常，情绪起伏较多</v>
+        <v>我是一个喜怒无常，情绪起伏较多的人</v>
       </c>
       <c r="B15" t="str">
         <v>BIG5</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>我是一个……的人 15. 善于创造，能找到聪明的方法来做事</v>
+        <v>我是一个善于创造，能找到聪明的方法来做事的人</v>
       </c>
       <c r="B16" t="str">
         <v>BIG5</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>我是一个……的人 16. 比较安静</v>
+        <v>我是一个比较安静的人</v>
       </c>
       <c r="B17" t="str">
         <v>BIG5</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>我是一个……的人 17. 对他人没有什么同情心</v>
+        <v>我是一个对他人没有什么同情心的人</v>
       </c>
       <c r="B18" t="str">
         <v>BIG5</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>我是一个……的人 18. 做事有计划有条理</v>
+        <v>我是一个做事有计划有条理的人</v>
       </c>
       <c r="B19" t="str">
         <v>BIG5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>我是一个……的人 19. 容易紧张</v>
+        <v>我是一个容易紧张的人</v>
       </c>
       <c r="B20" t="str">
         <v>BIG5</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>我是一个……的人 20. 着迷于艺术、音乐或文学</v>
+        <v>我是一个着迷于艺术、音乐或文学的人</v>
       </c>
       <c r="B21" t="str">
         <v>BIG5</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>我是一个……的人 21. 常常处于主导地位，像个领导一样</v>
+        <v>我是一个常常处于主导地位，像个领导一样的人</v>
       </c>
       <c r="B22" t="str">
         <v>BIG5</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>我是一个……的人 22. 常与他人意见不和</v>
+        <v>我是一个常与他人意见不和的人</v>
       </c>
       <c r="B23" t="str">
         <v>BIG5</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>我是一个……的人 23. 很难开始行动起来去完成一项任务</v>
+        <v>我是一个很难开始行动起来去完成一项任务的人</v>
       </c>
       <c r="B24" t="str">
         <v>BIG5</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>我是一个……的人 24. 觉得有安全感，对自己满意</v>
+        <v>我是一个觉得有安全感，对自己满意的人</v>
       </c>
       <c r="B25" t="str">
         <v>BIG5</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>我是一个……的人 25. 不喜欢知识性或者哲学性强的讨论</v>
+        <v>我是一个不喜欢知识性或者哲学性强的讨论的人</v>
       </c>
       <c r="B26" t="str">
         <v>BIG5</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>我是一个……的人 26. 不如别人有活力</v>
+        <v>我是一个不如别人有活力的人</v>
       </c>
       <c r="B27" t="str">
         <v>BIG5</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>我是一个……的人 27. 宽宏大量</v>
+        <v>我是一个宽宏大量的人</v>
       </c>
       <c r="B28" t="str">
         <v>BIG5</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>我是一个……的人 28. 有时比较没有责任心</v>
+        <v>我是一个有时比较没有责任心的人</v>
       </c>
       <c r="B29" t="str">
         <v>BIG5</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>我是一个……的人 29. 情绪稳定，不易生气</v>
+        <v>我是一个情绪稳定，不易生气的人</v>
       </c>
       <c r="B30" t="str">
         <v>BIG5</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>我是一个……的人 30. 几乎没有什么创造性</v>
+        <v>我是一个几乎没有什么创造性的人</v>
       </c>
       <c r="B31" t="str">
         <v>BIG5</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>我是一个……的人 31. 有时会害羞，比较内向</v>
+        <v>我是一个有时会害羞，比较内向的人</v>
       </c>
       <c r="B32" t="str">
         <v>BIG5</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>我是一个……的人 32. 乐于助人，待人无私</v>
+        <v>我是一个乐于助人，待人无私的人</v>
       </c>
       <c r="B33" t="str">
         <v>BIG5</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>我是一个……的人 33. 习惯让事物保持整洁有序</v>
+        <v>我是一个习惯让事物保持整洁有序的人</v>
       </c>
       <c r="B34" t="str">
         <v>BIG5</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>我是一个……的人 34. 时常忧心忡忡，担心很多事情</v>
+        <v>我是一个时常忧心忡忡，担心很多事情的人</v>
       </c>
       <c r="B35" t="str">
         <v>BIG5</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>我是一个……的人 35. 重视艺术与审美</v>
+        <v>我是一个重视艺术与审美的人</v>
       </c>
       <c r="B36" t="str">
         <v>BIG5</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>我是一个……的人 36. 感觉自己很难对他人产生影响</v>
+        <v>我是一个感觉自己很难对他人产生影响的人</v>
       </c>
       <c r="B37" t="str">
         <v>BIG5</v>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>我是一个……的人 37. 有时对人比较粗鲁</v>
+        <v>我是一个有时对人比较粗鲁的人</v>
       </c>
       <c r="B38" t="str">
         <v>BIG5</v>
@@ -1744,7 +1744,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>我是一个……的人 38. 有效率，做事有始有终</v>
+        <v>我是一个有效率，做事有始有终的人</v>
       </c>
       <c r="B39" t="str">
         <v>BIG5</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>我是一个……的人 39. 时常觉得悲伤</v>
+        <v>我是一个时常觉得悲伤的人</v>
       </c>
       <c r="B40" t="str">
         <v>BIG5</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>我是一个……的人 40. 思想深刻</v>
+        <v>我是一个思想深刻的人</v>
       </c>
       <c r="B41" t="str">
         <v>BIG5</v>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>我是一个……的人 41. 精力充沛</v>
+        <v>我是一个精力充沛的人</v>
       </c>
       <c r="B42" t="str">
         <v>BIG5</v>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>我是一个……的人 42. 不相信别人，怀疑别人的意图</v>
+        <v>我是一个不相信别人，怀疑别人的意图的人</v>
       </c>
       <c r="B43" t="str">
         <v>BIG5</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>我是一个……的人 43. 可靠的，总是值得他人信赖</v>
+        <v>我是一个可靠的，总是值得他人信赖的人</v>
       </c>
       <c r="B44" t="str">
         <v>BIG5</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>我是一个……的人 44. 能够控制自己的情绪</v>
+        <v>我是一个能够控制自己的情绪的人</v>
       </c>
       <c r="B45" t="str">
         <v>BIG5</v>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>我是一个……的人 45. 缺乏想象力</v>
+        <v>我是一个缺乏想象力的人</v>
       </c>
       <c r="B46" t="str">
         <v>BIG5</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>我是一个……的人 46. 爱说话，健谈</v>
+        <v>我是一个爱说话，健谈的人</v>
       </c>
       <c r="B47" t="str">
         <v>BIG5</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>我是一个……的人 47. 有时对人冷淡，漠不关心</v>
+        <v>我是一个有时对人冷淡，漠不关心的人</v>
       </c>
       <c r="B48" t="str">
         <v>BIG5</v>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>我是一个……的人 48. 乱糟糟的，不爱收拾</v>
+        <v>我是一个乱糟糟的，不爱收拾的人</v>
       </c>
       <c r="B49" t="str">
         <v>BIG5</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>我是一个……的人 49. 很少觉得焦虑或者害怕</v>
+        <v>我是一个很少觉得焦虑或者害怕的人</v>
       </c>
       <c r="B50" t="str">
         <v>BIG5</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>我是一个……的人 50. 觉得诗歌、戏剧很无聊</v>
+        <v>我是一个觉得诗歌、戏剧很无聊的人</v>
       </c>
       <c r="B51" t="str">
         <v>BIG5</v>
@@ -2199,7 +2199,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>我是一个……的人 51. 更喜欢让别人来领头负责</v>
+        <v>我是一个更喜欢让别人来领头负责的人</v>
       </c>
       <c r="B52" t="str">
         <v>BIG5</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>我是一个……的人 52. 待人谦逊礼让</v>
+        <v>我是一个待人谦逊礼让的人</v>
       </c>
       <c r="B53" t="str">
         <v>BIG5</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>我是一个……的人 53. 有恒心，能坚持把事情做完</v>
+        <v>我是一个有恒心，能坚持把事情做完的人</v>
       </c>
       <c r="B54" t="str">
         <v>BIG5</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>我是一个……的人 54. 时常觉得郁郁寡欢</v>
+        <v>我是一个时常觉得郁郁寡欢的人</v>
       </c>
       <c r="B55" t="str">
         <v>BIG5</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>我是一个……的人 55. 对抽象的概念和想法没什么兴趣</v>
+        <v>我是一个对抽象的概念和想法没什么兴趣的人</v>
       </c>
       <c r="B56" t="str">
         <v>BIG5</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>我是一个……的人 56. 充满热情</v>
+        <v>我是一个充满热情的人</v>
       </c>
       <c r="B57" t="str">
         <v>BIG5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>我是一个……的人 57. 把人往最好的方面想</v>
+        <v>我是一个把人往最好的方面想的人</v>
       </c>
       <c r="B58" t="str">
         <v>BIG5</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>我是一个……的人 58. 有时候会做出一些不负责任的行为</v>
+        <v>我是一个有时候会做出一些不负责任的行为的人</v>
       </c>
       <c r="B59" t="str">
         <v>BIG5</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>我是一个……的人 59. 情绪多变，容易愤怒</v>
+        <v>我是一个情绪多变，容易愤怒的人</v>
       </c>
       <c r="B60" t="str">
         <v>BIG5</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>我是一个……的人 60. 有创意，能想出新点子</v>
+        <v>我是一个有创意，能想出新点子的人</v>
       </c>
       <c r="B61" t="str">
         <v>BIG5</v>
